--- a/data/export/2026-09-22-operations.xlsx
+++ b/data/export/2026-09-22-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD23"/>
+  <dimension ref="A1:AD53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -454,7 +454,7 @@
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
     <col width="14" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
     <col width="18" customWidth="1" min="28" max="28"/>
@@ -648,24 +648,24 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:16</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>66分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>06:21采样：该车到重点站德川路华夏东路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -704,12 +704,12 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -719,22 +719,22 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>06:21采样：该车到重点站博兴路东陆路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -828,12 +828,12 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -896,29 +896,29 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>06:21采样：该车到重点站德川路华夏东路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -952,12 +952,12 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -967,22 +967,22 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>3/9</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -1020,29 +1020,29 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1101,12 +1101,12 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -1149,26 +1149,22 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数91分钟估算，约±12分钟</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：07:21采样，终点ETA 41分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1176,7 +1172,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1205,7 +1201,7 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1215,22 +1211,22 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>8/9</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -1285,12 +1281,12 @@
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±8分钟</t>
+          <t>07:21采样：该车到重点站唐陆公路唐镇路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±6分钟</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1300,7 +1296,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1329,7 +1325,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1354,7 +1350,7 @@
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>4/9</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -1397,22 +1393,26 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>07:21采样：该车到重点站唐陆公路创新路 ETA 37分钟；叠加该车自身同类时段从该站到终点历史中位数28分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1444,17 +1444,17 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1464,13 +1464,17 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -1513,24 +1517,24 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±8分钟</t>
+          <t>07:21采样：该车到重点站唐陆公路唐镇路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±11分钟</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1540,7 +1544,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1564,12 +1568,12 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -1589,12 +1593,12 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>6/9</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -1607,24 +1611,24 @@
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>沪A32298D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
-        </is>
-      </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -1637,34 +1641,34 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±8分钟</t>
+          <t>07:21采样：该车到重点站新德西路德翔路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1678,7 +1682,7 @@
       <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1693,7 +1697,7 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
@@ -1713,40 +1717,40 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>7/9</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1761,34 +1765,34 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>06:20采样：该车到重点站关岳路康达路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数130分钟，约±8分钟</t>
+          <t>07:21采样：该车到重点站东陆路金海路 ETA 22分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1802,7 +1806,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1837,40 +1841,40 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>3/8</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1885,34 +1889,34 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>06:20采样：该车到重点站莱阳路东陆路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数117分钟，约±13分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±6分钟</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1926,7 +1930,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1936,12 +1940,12 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -1961,40 +1965,40 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>1/8</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2009,34 +2013,34 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数135分钟估算，约±14分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±9分钟</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2050,7 +2054,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -2060,7 +2064,7 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
@@ -2075,50 +2079,50 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>2/8</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2133,30 +2137,34 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2170,7 +2178,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2180,17 +2188,17 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2200,41 +2208,45 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2249,30 +2261,34 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2286,7 +2302,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2296,17 +2312,17 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2316,41 +2332,45 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2365,30 +2385,34 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2402,7 +2426,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2412,61 +2436,65 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>78.5</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2481,34 +2509,34 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>160分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数160分钟估算，约±5分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±9分钟</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2522,7 +2550,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2547,22 +2575,22 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>4/8</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -2575,7 +2603,7 @@
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2585,7 +2613,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2605,34 +2633,34 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>160分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数160分钟估算，约±5分钟</t>
+          <t>07:20采样：该车到重点站迎春路金松路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±9分钟</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2646,7 +2674,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2661,7 +2689,7 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
@@ -2681,30 +2709,30 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>4/8</t>
+          <t>4/20</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2714,7 +2742,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2729,30 +2757,34 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：06:20采样，终点ETA 75分钟</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr"/>
+          <t>07:20采样：该车到重点站沪南路御桥路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±15分钟</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2776,17 +2808,17 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2796,41 +2828,45 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/5</t>
+          <t>1/20</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2845,34 +2881,34 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±12分钟</t>
+          <t>07:20采样：该车到重点站迎春路长柳路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数78分钟，约±13分钟</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2886,7 +2922,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2901,7 +2937,7 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -2921,40 +2957,40 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>3/20</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2987,12 +3023,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3006,7 +3042,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -3042,35 +3078,35 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/5</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3103,12 +3139,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3122,7 +3158,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3158,35 +3194,35 @@
       <c r="AC22" s="2" t="inlineStr"/>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/5</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:55</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3224,7 +3260,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3238,7 +3274,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:55</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3274,7 +3310,3691 @@
       <c r="AC23" s="2" t="inlineStr"/>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/5</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>141分钟</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站沪南路高科西路 ETA 25分钟；叠加该车自身同类时段从该站到终点历史中位数77分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>2/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>171分钟</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站金杨路金业路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数137分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>14/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>160分钟</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站康沈路秀康路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数131分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>9/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>177分钟</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站博兴路兰城路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数147分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>177.0</t>
+        </is>
+      </c>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>15/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>163分钟</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站川周公路康沈路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数142分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>163.0</t>
+        </is>
+      </c>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>10/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>155分钟</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站博兴路兰城路 ETA 28分钟；叠加该车自身同类时段从该站到终点历史中位数124分钟，约±14分钟</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>5/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>170分钟</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站关岳路康达路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数157分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>170.0</t>
+        </is>
+      </c>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>13/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>164分钟</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数164分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>164.0</t>
+        </is>
+      </c>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>11/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>157分钟</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数157分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>157.0</t>
+        </is>
+      </c>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>7/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>157分钟</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数157分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>157.0</t>
+        </is>
+      </c>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>7/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>166分钟</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数166分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>166.0</t>
+        </is>
+      </c>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>12/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>155分钟</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数155分钟估算，约±11分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>5/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>07:46</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>96分钟</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS末次终点ETA推算：07:20采样，终点ETA 26分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>96分钟</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站五莲路荷泽路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±11分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站金高路俱进路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±14分钟</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>93分钟</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站巨峰路成园路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站五莲路荷泽路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>06:55</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>111分钟</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站金高路俱进路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数71分钟，约±11分钟</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>06:55</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>111.0</t>
+        </is>
+      </c>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站五莲路荷泽路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±8分钟</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>114分钟</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站杨高北路夏碧路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±11分钟</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±11分钟</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>91分钟</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数91分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>97分钟</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数97分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-operations.xlsx
+++ b/data/export/2026-09-22-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD53"/>
+  <dimension ref="A1:AD79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
@@ -447,14 +447,14 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
     <col width="14" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
     <col width="18" customWidth="1" min="28" max="28"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -843,22 +843,22 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -901,24 +901,24 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1025,24 +1025,24 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1091,22 +1091,22 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1144,27 +1144,31 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：07:21采样，终点ETA 41分钟</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1172,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1196,12 +1200,12 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1226,7 +1230,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1264,29 +1268,29 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>07:21采样：该车到重点站唐陆公路唐镇路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1296,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1320,12 +1324,12 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1335,22 +1339,22 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1388,24 +1392,24 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>07:21采样：该车到重点站唐陆公路创新路 ETA 37分钟；叠加该车自身同类时段从该站到终点历史中位数28分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1420,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1444,12 +1448,12 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -1459,22 +1463,22 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1512,29 +1516,29 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>07:21采样：该车到重点站唐陆公路唐镇路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±11分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1544,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1568,12 +1572,12 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -1583,22 +1587,22 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1636,29 +1640,29 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>07:21采样：该车到重点站新德西路德翔路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1668,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1692,12 +1696,12 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
@@ -1707,22 +1711,22 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1760,29 +1764,29 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>07:21采样：该车到重点站东陆路金海路 ETA 22分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1792,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1816,12 +1820,12 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1831,22 +1835,22 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1889,26 +1893,22 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±6分钟</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:22采样，终点ETA 38分钟</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -2013,24 +2013,24 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±9分钟</t>
+          <t>08:22采样：该车到重点站唐陆公路川桥路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2137,24 +2137,24 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±14分钟</t>
+          <t>08:22采样：该车到重点站唐陆公路川桥路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数29分钟，约±6分钟</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
@@ -2213,12 +2213,12 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2261,24 +2261,24 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±12分钟</t>
+          <t>08:12采样：该车到重点站新德西路德川路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±6分钟</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2312,12 +2312,12 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2385,24 +2385,24 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±6分钟</t>
+          <t>08:22采样：该车到重点站唐陆公路川桥路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2479,24 +2479,24 @@
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A67026D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
-        </is>
-      </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -2509,24 +2509,24 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±9分钟</t>
+          <t>08:22采样：该车到重点站德川路华夏东路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±7分钟</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2550,7 +2550,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -2585,40 +2585,40 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2633,34 +2633,34 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站迎春路金松路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±9分钟</t>
+          <t>08:22采样：该车到重点站新川路华东路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2674,7 +2674,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2699,50 +2699,50 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>4/20</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2757,34 +2757,34 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站沪南路御桥路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±15分钟</t>
+          <t>08:22采样：该车到重点站博兴路东陆路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±11分钟</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2823,50 +2823,50 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>1/20</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A02126A</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2881,34 +2881,34 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站迎春路长柳路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数78分钟，约±13分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±14分钟</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2922,7 +2922,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -2957,40 +2957,40 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>3/20</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3005,30 +3005,34 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3042,7 +3046,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -3052,61 +3056,65 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3121,30 +3129,34 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数94分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3158,7 +3170,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3168,61 +3180,65 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>91.5</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3237,30 +3253,34 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr"/>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3274,7 +3294,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3284,61 +3304,65 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3353,34 +3377,34 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站沪南路高科西路 ETA 25分钟；叠加该车自身同类时段从该站到终点历史中位数77分钟，约±5分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±12分钟</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3394,7 +3418,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3404,12 +3428,12 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3419,50 +3443,50 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>2/20</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3477,34 +3501,34 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>171分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站金杨路金业路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数137分钟，约±5分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±8分钟</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3518,7 +3542,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3533,7 +3557,7 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3543,22 +3567,22 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>14/20</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3595,7 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3581,7 +3605,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3596,39 +3620,39 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>160分钟</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站康沈路秀康路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数131分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3642,7 +3666,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3652,12 +3676,12 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3667,22 +3691,22 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>9/20</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -3695,7 +3719,7 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3705,7 +3729,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3720,39 +3744,39 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>177分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站博兴路兰城路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数147分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3766,7 +3790,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3776,12 +3800,12 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3791,22 +3815,22 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>177.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>15/20</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -3819,24 +3843,24 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3844,39 +3868,39 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>163分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站川周公路康沈路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数142分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3890,7 +3914,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3900,12 +3924,12 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -3915,22 +3939,22 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>10/20</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3967,7 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3953,7 +3977,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3973,30 +3997,30 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>172分钟</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：08:21采样，终点ETA 61分钟</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4010,7 +4034,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4025,7 +4049,7 @@
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -4046,7 +4070,7 @@
       <c r="AC29" s="2" t="inlineStr"/>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4083,7 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -4069,7 +4093,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -4079,44 +4103,40 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq29推进至seq39，推进10站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>155分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站博兴路兰城路 ETA 28分钟；叠加该车自身同类时段从该站到终点历史中位数124分钟，约±14分钟</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4124,13 +4144,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr"/>
-      <c r="S30" s="2" t="inlineStr"/>
-      <c r="T30" s="2" t="inlineStr"/>
-      <c r="U30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>物理seq30（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>07:46</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq30映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4140,17 +4176,17 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4160,17 +4196,13 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr">
-        <is>
-          <t>155.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>5/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4183,24 +4215,24 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4213,34 +4245,30 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>170分钟</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站关岳路康达路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数157分钟，约±6分钟</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:21采样，终点ETA 56分钟</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4254,7 +4282,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4264,17 +4292,17 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4284,17 +4312,13 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr">
-        <is>
-          <t>170.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>13/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4307,7 +4331,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4317,7 +4341,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4337,30 +4361,34 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>08:21采样：该车到重点站锦绣路罗山路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4374,7 +4402,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4384,17 +4412,17 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4404,13 +4432,17 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4455,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4433,7 +4465,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4453,34 +4485,34 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>164分钟</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数164分钟估算，约±10分钟</t>
+          <t>08:21采样：该车到重点站沪南路北中路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±7分钟</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4494,7 +4526,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4509,7 +4541,7 @@
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -4529,12 +4561,12 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>11/20</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -4547,7 +4579,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4557,7 +4589,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4577,34 +4609,34 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>157分钟</t>
+          <t>169分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数157分钟估算，约±8分钟</t>
+          <t>08:21采样：该车到重点站锦绣路花木路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数82分钟，约±12分钟</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4618,7 +4650,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4628,12 +4660,12 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4653,12 +4685,12 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>157.0</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>7/20</t>
+          <t>17/27</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4703,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4681,7 +4713,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4701,34 +4733,34 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>157分钟</t>
+          <t>168分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数157分钟估算，约±8分钟</t>
+          <t>08:21采样：该车到重点站迎春路长柳路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数90分钟，约±11分钟</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4742,7 +4774,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4752,12 +4784,12 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4777,12 +4809,12 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>157.0</t>
+          <t>168.0</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>7/20</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -4795,7 +4827,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4805,7 +4837,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4825,19 +4857,19 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>166分钟</t>
+          <t>164分钟</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数166分钟估算，约±10分钟</t>
+          <t>08:21采样：该车到重点站沪南路高科西路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数83分钟，约±10分钟</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4847,12 +4879,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4866,7 +4898,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4881,7 +4913,7 @@
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4901,12 +4933,12 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>12/20</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -4919,24 +4951,24 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4949,34 +4981,30 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>155分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数155分钟估算，约±11分钟</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4990,7 +5018,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -5000,17 +5028,17 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -5020,45 +5048,41 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr">
-        <is>
-          <t>155.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>5/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -5073,30 +5097,34 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：07:20采样，终点ETA 26分钟</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>08:21采样：该车到重点站丁香路锦绣路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数82分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5110,7 +5138,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5120,12 +5148,12 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -5135,50 +5163,50 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5193,34 +5221,34 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>164分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站五莲路荷泽路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±11分钟</t>
+          <t>07:31采样：该车到重点站川周公路康沈路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数147分钟，约±6分钟</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5234,7 +5262,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5244,7 +5272,7 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
@@ -5269,40 +5297,40 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5317,34 +5345,30 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站金高路俱进路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±14分钟</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5358,7 +5382,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5368,17 +5392,17 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5388,45 +5412,41 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr">
-        <is>
-          <t>89.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5441,34 +5461,34 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站巨峰路成园路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±5分钟</t>
+          <t>08:21采样：该车到重点站白桦路明月路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数103分钟，约±10分钟</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5482,7 +5502,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5517,40 +5537,40 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5565,30 +5585,34 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>171分钟</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr"/>
+          <t>08:21采样：该车到重点站沪南路华夏西路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数102分钟，约±14分钟</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5602,7 +5626,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5612,17 +5636,17 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5632,41 +5656,45 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC42" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>18/27</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5681,34 +5709,34 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站五莲路荷泽路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±5分钟</t>
+          <t>08:21采样：该车到重点站金杨路金业路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数120分钟，约±8分钟</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5722,7 +5750,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5757,40 +5785,40 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>06:55</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5805,34 +5833,34 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>111分钟</t>
+          <t>174分钟</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站金高路俱进路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数71分钟，约±11分钟</t>
+          <t>08:21采样：该车到重点站康沈路秀康路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数133分钟，约±15分钟</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5846,7 +5874,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>06:55</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5881,40 +5909,40 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>174.0</t>
         </is>
       </c>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>19/27</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5929,34 +5957,34 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站五莲路荷泽路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±8分钟</t>
+          <t>08:21采样：该车到重点站金杨路金业路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±12分钟</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5970,7 +5998,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5980,7 +6008,7 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
@@ -6005,40 +6033,40 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -6053,34 +6081,34 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>114分钟</t>
+          <t>166分钟</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站杨高北路夏碧路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±11分钟</t>
+          <t>08:21采样：该车到重点站康沈路秀康路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数136分钟，约±15分钟</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6094,7 +6122,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -6129,40 +6157,40 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>15/27</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -6177,34 +6205,34 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr"/>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±10分钟</t>
+          <t>08:21采样：该车到重点站莱阳路东陆路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数128分钟，约±9分钟</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6218,7 +6246,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6233,7 +6261,7 @@
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
@@ -6253,40 +6281,40 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A58633D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6319,12 +6347,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6338,7 +6366,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6374,35 +6402,35 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6417,34 +6445,34 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr"/>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±11分钟</t>
+          <t>08:21采样：该车到重点站康丽路康恩路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数146分钟，约±10分钟</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6458,7 +6486,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6468,12 +6496,12 @@
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -6493,40 +6521,40 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6541,34 +6569,30 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr"/>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±9分钟</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6582,7 +6606,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6592,17 +6616,17 @@
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6612,45 +6636,41 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC50" s="2" t="inlineStr">
-        <is>
-          <t>92.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6665,34 +6685,34 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr"/>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数91分钟估算，约±8分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数158分钟估算，约±5分钟</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6706,7 +6726,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6741,40 +6761,40 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6789,34 +6809,30 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr"/>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数97分钟估算，约±6分钟</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6830,7 +6846,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6840,17 +6856,17 @@
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6860,45 +6876,41 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC52" s="2" t="inlineStr">
-        <is>
-          <t>97.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6913,34 +6925,34 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±8分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数139分钟估算，约±14分钟</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6954,47 +6966,3247 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>133.5</t>
+        </is>
+      </c>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>1/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>142分钟</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数142分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>147.5</t>
+        </is>
+      </c>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>5/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>144分钟</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数144分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>2/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>91分钟</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>109分钟</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>99.5</t>
+        </is>
+      </c>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>108分钟</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>同车下一次反向发车08:45，减去该车自身同类时段历史终点停站中位数16分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>同车反向发车反推</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>96分钟</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>94.5</t>
+        </is>
+      </c>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>91分钟</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>90.5</t>
+        </is>
+      </c>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>06:55</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>99分钟</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>08:10采样：该车到重点站金杨路云山路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数16分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>06:55</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>96分钟</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS末次终点ETA推算：08:20采样，终点ETA 15分钟</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>111分钟</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>08:20采样：该车到重点站张杨北路博兴路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数31分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>111.0</t>
+        </is>
+      </c>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>100分钟</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>08:20采样：该车到重点站杨高北路（外高桥保税区南站） ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数30分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>112分钟</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>08:20采样：该车到重点站张杨北路博兴路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±9分钟</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>08:20采样：该车到重点站五莲路归昌路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数25分钟，约±12分钟</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>99分钟</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>08:20采样：该车到重点站金高路行泰路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>08:20采样：该车到重点站金高路东靖路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>102分钟</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>08:20采样：该车到重点站五莲路凌河路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A66373D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
           <t>08:03</t>
         </is>
       </c>
-      <c r="W53" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>08:20采样：该车到重点站张杨北路金桥路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X53" s="2" t="inlineStr">
+      <c r="X72" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Y53" s="2" t="inlineStr">
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>93分钟</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>08:20采样：该车到重点站花山路大同路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数78分钟，约±10分钟</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>93分钟</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数93分钟估算，约±15分钟</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Z53" s="2" t="inlineStr">
+      <c r="Z74" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
+      <c r="AA74" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB53" s="2" t="inlineStr">
+      <c r="AB74" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AC53" s="2" t="inlineStr">
-        <is>
-          <t>92.0</t>
-        </is>
-      </c>
-      <c r="AD53" s="2" t="inlineStr">
-        <is>
-          <t>6/15</t>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>94.5</t>
+        </is>
+      </c>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>99.5</t>
+        </is>
+      </c>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>90.5</t>
+        </is>
+      </c>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-operations.xlsx
+++ b/data/export/2026-09-22-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD79"/>
+  <dimension ref="A1:AD88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -452,9 +452,9 @@
     <col width="20" customWidth="1" min="20" max="20"/>
     <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
     <col width="14" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
     <col width="18" customWidth="1" min="28" max="28"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -719,22 +719,22 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1101,12 +1101,12 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1645,24 +1645,24 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1721,12 +1721,12 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1769,24 +1769,24 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1898,17 +1898,21 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:22采样，终点ETA 38分钟</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1916,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1940,12 +1944,12 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -1955,22 +1959,22 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2008,12 +2012,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2025,12 +2029,12 @@
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>08:22采样：该车到重点站唐陆公路川桥路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -2040,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2064,12 +2068,12 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
@@ -2079,22 +2083,22 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2137,24 +2141,24 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>08:22采样：该车到重点站唐陆公路川桥路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数29分钟，约±6分钟</t>
+          <t>08:43采样：该车到重点站佳林路金高路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数22分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -2164,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2213,12 +2217,12 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -2261,24 +2265,24 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>08:12采样：该车到重点站新德西路德川路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±6分钟</t>
+          <t>08:43采样：该车到重点站唐陆公路锦绣东路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -2288,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2337,7 +2341,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
@@ -2385,7 +2389,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2397,12 +2401,12 @@
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>08:22采样：该车到重点站唐陆公路川桥路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±5分钟</t>
+          <t>08:43采样：该车到重点站唐陆公路春雅路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数39分钟，约±7分钟</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2412,7 +2416,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2466,7 +2470,7 @@
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2513,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2521,12 +2525,12 @@
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>08:22采样：该车到重点站德川路华夏东路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±7分钟</t>
+          <t>08:43采样：该车到重点站唐陆公路锦绣东路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2536,7 +2540,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2590,7 +2594,7 @@
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2633,19 +2637,19 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>08:22采样：该车到重点站新川路华东路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±5分钟</t>
+          <t>08:43采样：该车到重点站唐陆公路唐镇路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2660,7 +2664,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2709,12 +2713,12 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2761,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2769,12 +2773,12 @@
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>08:22采样：该车到重点站博兴路东陆路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±11分钟</t>
+          <t>08:43采样：该车到重点站唐陆公路春雅路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2784,7 +2788,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2808,7 +2812,7 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
@@ -2838,7 +2842,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2881,19 +2885,19 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±14分钟</t>
+          <t>08:43采样：该车到重点站唐陆公路唐镇路 ETA 21分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±14分钟</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2908,7 +2912,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2937,7 +2941,7 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -2957,12 +2961,12 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -3005,19 +3009,19 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±8分钟</t>
+          <t>08:43采样：该车到重点站东陆路金海路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±8分钟</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -3032,7 +3036,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3061,7 +3065,7 @@
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -3081,12 +3085,12 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3160,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3280,7 +3284,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3334,7 +3338,7 @@
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3408,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3453,12 +3457,12 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3528,7 +3532,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3577,40 +3581,40 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3620,39 +3624,39 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±8分钟</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3666,7 +3670,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3676,12 +3680,12 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3701,40 +3705,40 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3744,39 +3748,39 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±8分钟</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3790,7 +3794,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3800,12 +3804,12 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3815,22 +3819,22 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3843,24 +3847,24 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>06:26</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3873,24 +3877,24 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -3900,7 +3904,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3914,7 +3918,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3949,12 +3953,12 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -3967,24 +3971,24 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>06:30</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3992,27 +3996,31 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>172分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:21采样，终点ETA 61分钟</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4020,7 +4028,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4034,7 +4042,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4044,33 +4052,37 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>133.5</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4095,7 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -4093,7 +4105,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -4103,32 +4115,36 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq29推进至seq39，推进10站，达到≥2站确认条件</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4136,7 +4152,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4144,29 +4160,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>物理seq30（站名待映射）</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>07:46</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>折返点按重建物理位置seq30映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
-        </is>
-      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4176,33 +4176,37 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -4215,24 +4219,24 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>06:41</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4245,30 +4249,30 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>156分钟</t>
+          <t>170分钟</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:21采样，终点ETA 56分钟</t>
+          <t>SHMAAS末次终点ETA推算：08:41采样，终点ETA 38分钟</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4282,7 +4286,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4292,33 +4296,37 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -4331,56 +4339,52 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq29推进至seq49，推进20站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>149分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站锦绣路罗山路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4388,7 +4392,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4396,13 +4400,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R32" s="2" t="inlineStr"/>
-      <c r="S32" s="2" t="inlineStr"/>
-      <c r="T32" s="2" t="inlineStr"/>
-      <c r="U32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>物理seq30（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>07:46</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq30映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4412,37 +4432,33 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr">
-        <is>
-          <t>149.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4471,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4465,7 +4481,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4485,34 +4501,30 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>156分钟</t>
+          <t>161分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站沪南路北中路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±7分钟</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:41采样，终点ETA 40分钟</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4526,7 +4538,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4536,12 +4548,12 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -4551,22 +4563,22 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB33" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>14/27</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4591,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4589,7 +4601,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4609,29 +4621,29 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>169分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站锦绣路花木路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数82分钟，约±12分钟</t>
+          <t>08:21采样：该车到重点站锦绣路罗山路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4650,7 +4662,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4660,7 +4672,7 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
@@ -4685,12 +4697,12 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>17/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4715,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4713,7 +4725,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4733,34 +4745,34 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>168分钟</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站迎春路长柳路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数90分钟，约±11分钟</t>
+          <t>08:41采样：该车到重点站康沈路秀沿路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数34分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4774,7 +4786,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4784,7 +4796,7 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
@@ -4809,12 +4821,12 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -4827,7 +4839,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4837,7 +4849,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4857,34 +4869,34 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>164分钟</t>
+          <t>168分钟</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站沪南路高科西路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数83分钟，约±10分钟</t>
+          <t>08:41采样：该车到重点站云山路碧云路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4898,7 +4910,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4933,12 +4945,12 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>168.0</t>
         </is>
       </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>15/27</t>
         </is>
       </c>
     </row>
@@ -4951,24 +4963,24 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:12</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4981,30 +4993,34 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>169分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>08:41采样：该车到重点站沪南路北中路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±12分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5018,7 +5034,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -5028,17 +5044,17 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -5048,13 +5064,17 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>169.0</t>
+        </is>
+      </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -5067,24 +5087,24 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5097,34 +5117,34 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>149分钟</t>
+          <t>169分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站丁香路锦绣路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数82分钟，约±7分钟</t>
+          <t>08:41采样：该车到重点站锦绣路罗山路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5138,7 +5158,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5173,12 +5193,12 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5211,7 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5201,7 +5221,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -5221,34 +5241,30 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>164分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>07:31采样：该车到重点站川周公路康沈路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数147分钟，约±6分钟</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5262,7 +5278,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5272,17 +5288,17 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5292,17 +5308,13 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr">
-        <is>
-          <t>164.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -5315,24 +5327,24 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>07:24</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5345,30 +5357,34 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr"/>
+          <t>08:41采样：该车到重点站浦建路锦绣路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±11分钟</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5382,7 +5398,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5392,17 +5408,17 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5412,13 +5428,17 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -5431,24 +5451,24 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5461,24 +5481,24 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>159分钟</t>
+          <t>170分钟</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站白桦路明月路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数103分钟，约±10分钟</t>
+          <t>08:41采样：该车到重点站锦绣路花木路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数79分钟，约±8分钟</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -5488,7 +5508,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5502,7 +5522,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5537,12 +5557,12 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>170.0</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>18/27</t>
         </is>
       </c>
     </row>
@@ -5555,7 +5575,7 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5565,7 +5585,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5585,34 +5605,30 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>171分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站沪南路华夏西路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数102分钟，约±14分钟</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5626,7 +5642,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5636,17 +5652,17 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5656,17 +5672,13 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC42" s="2" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>18/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -5679,7 +5691,7 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5689,7 +5701,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5709,34 +5721,34 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>160分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站金杨路金业路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数120分钟，约±8分钟</t>
+          <t>08:41采样：该车到重点站迎春路长柳路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数79分钟，约±10分钟</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5750,7 +5762,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5785,12 +5797,12 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -5803,7 +5815,7 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5813,7 +5825,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5833,24 +5845,24 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>174分钟</t>
+          <t>170分钟</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站康沈路秀康路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数133分钟，约±15分钟</t>
+          <t>08:41采样：该车到重点站沪南路高科西路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±11分钟</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -5860,7 +5872,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5874,7 +5886,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5909,12 +5921,12 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>174.0</t>
+          <t>170.0</t>
         </is>
       </c>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>19/27</t>
+          <t>18/27</t>
         </is>
       </c>
     </row>
@@ -5927,7 +5939,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5937,7 +5949,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5957,19 +5969,19 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>147分钟</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站金杨路金业路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±12分钟</t>
+          <t>08:41采样：该车到重点站丁香路锦绣路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±12分钟</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5979,12 +5991,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5998,7 +6010,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -6033,12 +6045,12 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -6051,7 +6063,7 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -6061,7 +6073,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -6081,19 +6093,19 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>166分钟</t>
+          <t>183分钟</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站康沈路秀康路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数136分钟，约±15分钟</t>
+          <t>08:31采样：该车到重点站康沈路秀康路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数133分钟，约±15分钟</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -6103,12 +6115,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6122,7 +6134,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -6157,12 +6169,12 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>183.0</t>
         </is>
       </c>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>21/27</t>
         </is>
       </c>
     </row>
@@ -6175,7 +6187,7 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -6185,7 +6197,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -6205,19 +6217,19 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>147分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr"/>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站莱阳路东陆路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数128分钟，约±9分钟</t>
+          <t>08:41采样：该车到重点站白桦路明月路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数91分钟，约±9分钟</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -6227,12 +6239,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6246,7 +6258,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6281,7 +6293,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AD47" s="2" t="inlineStr">
@@ -6299,7 +6311,7 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -6309,7 +6321,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -6329,30 +6341,34 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>173分钟</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr"/>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="inlineStr"/>
+          <t>08:41采样：该车到重点站沪南路华夏西路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数108分钟，约±12分钟</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6366,7 +6382,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6376,17 +6392,17 @@
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6396,13 +6412,17 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC48" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>173.0</t>
+        </is>
+      </c>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>20/27</t>
         </is>
       </c>
     </row>
@@ -6415,24 +6435,24 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -6445,34 +6465,34 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>149分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr"/>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站康丽路康恩路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数146分钟，约±10分钟</t>
+          <t>08:41采样：该车到重点站金杨路云山路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数97分钟，约±8分钟</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6486,7 +6506,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6521,12 +6541,12 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -6539,22 +6559,22 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>08:20</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6592,7 +6612,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6606,7 +6626,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6655,7 +6675,7 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -6665,7 +6685,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -6685,34 +6705,34 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>158分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr"/>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数158分钟估算，约±5分钟</t>
+          <t>08:41采样：该车到重点站康沈路秀康路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数121分钟，约±7分钟</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6726,7 +6746,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6741,7 +6761,7 @@
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6761,12 +6781,12 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -6779,7 +6799,7 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -6789,7 +6809,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -6832,7 +6852,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6846,7 +6866,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6895,7 +6915,7 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -6905,7 +6925,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -6925,24 +6945,24 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数139分钟估算，约±14分钟</t>
+          <t>08:41采样：该车到重点站川周公路康沈路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数138分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
@@ -6952,7 +6972,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6966,7 +6986,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6976,12 +6996,12 @@
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6991,22 +7011,22 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -7019,7 +7039,7 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -7029,7 +7049,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -7049,26 +7069,22 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr"/>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数142分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7076,7 +7092,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -7090,7 +7106,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -7100,37 +7116,33 @@
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC54" s="2" t="inlineStr">
-        <is>
-          <t>147.5</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -7143,7 +7155,7 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -7153,7 +7165,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -7173,24 +7185,24 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr"/>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数144分钟估算，约±8分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数139分钟估算，约±14分钟</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
@@ -7200,7 +7212,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7214,7 +7226,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7224,7 +7236,7 @@
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
@@ -7249,40 +7261,40 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -7292,39 +7304,39 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数142分钟估算，约±5分钟</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7338,7 +7350,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7348,12 +7360,12 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -7373,40 +7385,40 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -7416,39 +7428,39 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>109分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数144分钟估算，约±8分钟</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7462,7 +7474,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7472,12 +7484,12 @@
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7497,40 +7509,40 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -7545,34 +7557,34 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>108分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车08:45，减去该车自身同类时段历史终点停站中位数16分钟，约±6分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数146分钟估算，约±8分钟</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7586,12 +7598,12 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>计划发车</t>
+          <t>终点确认到达+2分钟（覆盖计划时间）</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
@@ -7601,7 +7613,7 @@
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7621,40 +7633,40 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -7664,39 +7676,35 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7710,7 +7718,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7720,17 +7728,17 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7740,45 +7748,41 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC59" s="2" t="inlineStr">
-        <is>
-          <t>94.5</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr"/>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7811,12 +7815,12 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7830,7 +7834,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7855,18 +7859,22 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB60" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
+      </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>14/27</t>
         </is>
       </c>
     </row>
@@ -7879,24 +7887,24 @@
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>06:50</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -7909,7 +7917,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7931,12 +7939,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7950,7 +7958,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7985,12 +7993,12 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -8003,7 +8011,7 @@
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -8013,7 +8021,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>06:55</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -8028,39 +8036,39 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>99分钟</t>
+          <t>109分钟</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr"/>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站金杨路云山路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数16分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8074,7 +8082,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>06:55</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -8084,12 +8092,12 @@
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -8099,22 +8107,22 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8127,24 +8135,24 @@
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -8152,35 +8160,39 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>113分钟</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr"/>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:20采样，终点ETA 15分钟</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8194,7 +8206,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -8204,12 +8216,12 @@
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -8224,17 +8236,17 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8247,24 +8259,24 @@
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>07:10</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -8272,29 +8284,29 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>111分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr"/>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站张杨北路博兴路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数31分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
@@ -8304,7 +8316,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8318,7 +8330,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8328,12 +8340,12 @@
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8343,22 +8355,22 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8371,24 +8383,24 @@
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -8401,34 +8413,30 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>100分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr"/>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站杨高北路（外高桥保税区南站） ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数30分钟，约±7分钟</t>
-        </is>
-      </c>
-      <c r="N65" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8442,7 +8450,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8452,17 +8460,17 @@
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
@@ -8472,17 +8480,13 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC65" s="2" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr"/>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -8495,24 +8499,24 @@
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A58633D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>07:20</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -8520,39 +8524,39 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>112分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr"/>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站张杨北路博兴路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±9分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8566,7 +8570,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8576,12 +8580,12 @@
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8591,22 +8595,22 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -8619,7 +8623,7 @@
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -8629,7 +8633,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:55</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -8644,39 +8648,39 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>114分钟</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr"/>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站五莲路归昌路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数25分钟，约±12分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8690,7 +8694,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:55</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8700,12 +8704,12 @@
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8715,22 +8719,22 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB67" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8743,7 +8747,7 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -8753,7 +8757,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -8768,24 +8772,24 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>99分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr"/>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站金高路行泰路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8795,12 +8799,12 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8814,7 +8818,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8824,12 +8828,12 @@
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
@@ -8839,22 +8843,22 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB68" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8867,7 +8871,7 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -8877,7 +8881,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -8897,34 +8901,30 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>117分钟</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr"/>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站金高路东靖路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N69" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:40采样，终点ETA 26分钟</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8938,7 +8938,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
@@ -8963,22 +8963,22 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8991,7 +8991,7 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -9016,39 +9016,39 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>102分钟</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站五莲路凌河路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -9062,7 +9062,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
@@ -9087,22 +9087,22 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB70" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9115,7 +9115,7 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A66373D</t>
+          <t>沪A58633D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -9145,30 +9145,34 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>105分钟</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N71" s="2" t="inlineStr"/>
+          <t>08:40采样：该车到重点站丁香路金松路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数6分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9182,7 +9186,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -9192,17 +9196,17 @@
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -9212,13 +9216,17 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC71" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -9231,24 +9239,24 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>08:03</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -9261,34 +9269,34 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站张杨北路金桥路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
+          <t>08:20采样：该车到重点站五莲路归昌路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数25分钟，约±12分钟</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9302,7 +9310,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9312,7 +9320,7 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
@@ -9327,22 +9335,22 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -9355,24 +9363,24 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -9385,26 +9393,22 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站花山路大同路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数78分钟，约±10分钟</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:40采样，终点ETA 30分钟</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr"/>
       <c r="O73" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -9412,7 +9416,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9426,7 +9430,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9436,12 +9440,12 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
@@ -9451,22 +9455,22 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9483,7 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A53629D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -9489,7 +9493,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -9509,7 +9513,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -9521,22 +9525,22 @@
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数93分钟估算，约±15分钟</t>
+          <t>08:40采样：该车到重点站五莲路荷泽路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数31分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9550,7 +9554,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9560,12 +9564,12 @@
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
@@ -9575,22 +9579,22 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9603,7 +9607,7 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -9613,7 +9617,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -9633,24 +9637,24 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±9分钟</t>
+          <t>08:40采样：该车到重点站金高路俱进路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±6分钟</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
@@ -9660,7 +9664,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9674,7 +9678,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9689,7 +9693,7 @@
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
@@ -9699,22 +9703,22 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9727,7 +9731,7 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A66373D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -9737,7 +9741,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -9757,34 +9761,30 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±6分钟</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9798,7 +9798,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9808,37 +9808,33 @@
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC76" s="2" t="inlineStr">
-        <is>
-          <t>90.5</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr"/>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -9851,7 +9847,7 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -9861,7 +9857,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -9881,34 +9877,34 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±14分钟</t>
+          <t>08:40采样：该车到重点站巨峰路成园路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数45分钟，约±8分钟</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9922,7 +9918,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9932,12 +9928,12 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -9947,22 +9943,22 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9975,24 +9971,24 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A57902D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -10005,34 +10001,34 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±12分钟</t>
+          <t>08:40采样：该车到重点站金高路俱进路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10046,7 +10042,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -10056,12 +10052,12 @@
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -10071,22 +10067,22 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -10099,7 +10095,7 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -10109,7 +10105,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -10129,22 +10125,26 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>107分钟</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="inlineStr"/>
+          <t>08:40采样：该车到重点站杨高北路夏碧路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数77分钟，约±13分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -10152,7 +10152,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10166,45 +10166,1149 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>101.5</t>
+        </is>
+      </c>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>91分钟</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>08:40采样：该车到重点站五莲路荷泽路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>90.5</t>
+        </is>
+      </c>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>08:40采样：该车到重点站五莲路荷泽路 ETA 26分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD82" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="W79" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X79" s="2" t="inlineStr">
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>101.5</t>
+        </is>
+      </c>
+      <c r="AD83" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y79" s="2" t="inlineStr">
+      <c r="Y84" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Z79" s="2" t="inlineStr">
+      <c r="Z84" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA79" s="2" t="inlineStr">
+      <c r="AA84" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB79" s="2" t="inlineStr">
+      <c r="AB84" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC79" s="2" t="inlineStr">
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
+      <c r="AD85" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AD86" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>91分钟</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数91分钟估算，约±11分钟</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="AD87" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>91分钟</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数91分钟估算，约±15分钟</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
         <is>
           <t>96.0</t>
         </is>
       </c>
-      <c r="AD79" s="2" t="inlineStr">
+      <c r="AD88" s="2" t="inlineStr">
         <is>
           <t>8/18</t>
         </is>

--- a/data/export/2026-09-22-operations.xlsx
+++ b/data/export/2026-09-22-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD88"/>
+  <dimension ref="A1:AD99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -452,7 +452,7 @@
     <col width="20" customWidth="1" min="20" max="20"/>
     <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="14" customWidth="1" min="26" max="26"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -967,22 +967,22 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1101,12 +1101,12 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1215,22 +1215,22 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1893,24 +1893,24 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
@@ -2017,24 +2017,24 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>100分钟</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
@@ -2136,29 +2136,29 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>100分钟</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>08:43采样：该车到重点站佳林路金高路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数22分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2192,12 +2192,12 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
@@ -2207,22 +2207,22 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2260,29 +2260,29 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>08:43采样：该车到重点站唐陆公路锦绣东路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2316,12 +2316,12 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
@@ -2331,22 +2331,22 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -2384,29 +2384,29 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>08:43采样：该车到重点站唐陆公路春雅路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数39分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -2455,22 +2455,22 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2513,26 +2513,22 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>08:43采样：该车到重点站唐陆公路锦绣东路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:14采样，终点ETA 19分钟</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2540,7 +2536,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2569,7 +2565,7 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -2589,12 +2585,12 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2637,19 +2633,19 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>08:43采样：该车到重点站唐陆公路唐镇路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±5分钟</t>
+          <t>09:03采样：该车到重点站唐陆公路川桥路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2664,7 +2660,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2713,12 +2709,12 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2761,26 +2757,22 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>08:43采样：该车到重点站唐陆公路春雅路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:14采样，终点ETA 27分钟</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2788,7 +2780,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2812,12 +2804,12 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -2827,22 +2819,22 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2885,24 +2877,24 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>08:43采样：该车到重点站唐陆公路唐镇路 ETA 21分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±14分钟</t>
+          <t>09:03采样：该车到重点站唐陆公路龙东大道 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±8分钟</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2912,7 +2904,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2936,7 +2928,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
@@ -2961,12 +2953,12 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3009,24 +3001,24 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>08:43采样：该车到重点站东陆路金海路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±8分钟</t>
+          <t>09:14采样：该车到重点站唐陆公路锦绣东路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -3036,7 +3028,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3085,12 +3077,12 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3133,24 +3125,24 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数94分钟估算，约±12分钟</t>
+          <t>09:03采样：该车到重点站新川路华东路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数83分钟，约±11分钟</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -3160,7 +3152,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3189,7 +3181,7 @@
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -3209,12 +3201,12 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3276,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3338,7 +3330,7 @@
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3381,24 +3373,24 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±12分钟</t>
+          <t>09:14采样：该车到重点站唐陆公路创新路 ETA 28分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -3408,7 +3400,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3432,12 +3424,12 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3457,12 +3449,12 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3532,7 +3524,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3656,7 +3648,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3705,7 +3697,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
@@ -3780,7 +3772,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3829,7 +3821,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
@@ -3841,28 +3833,28 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3872,39 +3864,39 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>152分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±10分钟</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3918,7 +3910,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3928,12 +3920,12 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -3953,40 +3945,40 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3996,39 +3988,35 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4042,7 +4030,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4052,17 +4040,17 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -4072,45 +4060,45 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -4120,39 +4108,39 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数70分钟估算，约±5分钟</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4166,7 +4154,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4176,12 +4164,12 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -4191,50 +4179,50 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4249,30 +4237,34 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>170分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:41采样，终点ETA 38分钟</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数77分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4286,7 +4278,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4301,7 +4293,7 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4311,22 +4303,22 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4339,52 +4331,56 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>06:36</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq29推进至seq49，推进20站，达到≥2站确认条件</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4392,7 +4388,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4400,29 +4396,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>物理seq30（站名待映射）</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>07:46</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>折返点按重建物理位置seq30映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
-        </is>
-      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4432,17 +4412,17 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4452,13 +4432,17 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -4471,7 +4455,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4481,7 +4465,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4496,35 +4480,39 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>161分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:41采样，终点ETA 40分钟</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4538,7 +4526,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4548,12 +4536,12 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -4568,17 +4556,17 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>14/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -4591,24 +4579,24 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4616,29 +4604,29 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>149分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站锦绣路罗山路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -4648,7 +4636,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4662,7 +4650,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4672,12 +4660,12 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4687,22 +4675,22 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -4715,24 +4703,24 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4740,39 +4728,39 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>151分钟</t>
+          <t>163分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>08:41采样：该车到重点站康沈路秀沿路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数34分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4786,7 +4774,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4796,12 +4784,12 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4811,22 +4799,22 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>154.5</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -4839,64 +4827,60 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq29推进至seq64，推进35站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>168分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>08:41采样：该车到重点站云山路碧云路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4904,13 +4888,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R36" s="2" t="inlineStr"/>
-      <c r="S36" s="2" t="inlineStr"/>
-      <c r="T36" s="2" t="inlineStr"/>
-      <c r="U36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>物理seq30（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>07:46</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq30映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4920,37 +4920,33 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr">
-        <is>
-          <t>168.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4963,7 +4959,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4973,7 +4969,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4993,34 +4989,30 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>169分钟</t>
+          <t>162分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>08:41采样：该车到重点站沪南路北中路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±12分钟</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:12采样，终点ETA 11分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5034,7 +5026,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -5044,12 +5036,12 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -5059,22 +5051,22 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB37" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>15/27</t>
         </is>
       </c>
     </row>
@@ -5087,7 +5079,7 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -5097,7 +5089,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -5117,19 +5109,19 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>169分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>08:41采样：该车到重点站锦绣路罗山路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
+          <t>同车下一次反向发车09:30，减去该车自身同类时段历史终点停站中位数18分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -5139,12 +5131,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5158,7 +5150,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5173,7 +5165,7 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -5183,22 +5175,22 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -5211,24 +5203,24 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>07:12</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5236,35 +5228,39 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5278,7 +5274,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5288,33 +5284,37 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -5327,24 +5327,24 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5357,34 +5357,34 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>154分钟</t>
+          <t>165分钟</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>08:41采样：该车到重点站浦建路锦绣路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±11分钟</t>
+          <t>09:12采样：该车到重点站五莲路兰城路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数27分钟，约±6分钟</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5398,7 +5398,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5408,7 +5408,7 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
@@ -5433,12 +5433,12 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>17/27</t>
         </is>
       </c>
     </row>
@@ -5451,24 +5451,24 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5481,34 +5481,34 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>170分钟</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>08:41采样：该车到重点站锦绣路花木路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数79分钟，约±8分钟</t>
+          <t>09:12采样：该车到重点站康沈路秀沿路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数34分钟，约±7分钟</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5522,7 +5522,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5547,22 +5547,22 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>170.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>18/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -5575,7 +5575,7 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5585,7 +5585,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5605,30 +5605,34 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>168分钟</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr"/>
+          <t>09:12采样：该车到重点站金杨路金口路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5642,7 +5646,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5652,17 +5656,17 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5672,13 +5676,17 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC42" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>19/27</t>
         </is>
       </c>
     </row>
@@ -5691,64 +5699,60 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq38推进至seq47，推进9站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>152分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>08:41采样：该车到重点站迎春路长柳路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数79分钟，约±10分钟</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5756,13 +5760,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R43" s="2" t="inlineStr"/>
-      <c r="S43" s="2" t="inlineStr"/>
-      <c r="T43" s="2" t="inlineStr"/>
-      <c r="U43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>08:26</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq23映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq38（站名待映射） ETA 9分钟参与校验</t>
+        </is>
+      </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5772,17 +5792,17 @@
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5792,17 +5812,13 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC43" s="2" t="inlineStr">
-        <is>
-          <t>152.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -5815,24 +5831,24 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5845,34 +5861,34 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>170分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>08:41采样：该车到重点站沪南路高科西路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±11分钟</t>
+          <t>08:51采样：该车到重点站沪南路北中路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±9分钟</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5886,7 +5902,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5896,7 +5912,7 @@
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
@@ -5921,12 +5937,12 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>170.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>18/27</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -5939,24 +5955,24 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5969,34 +5985,34 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>154分钟</t>
+          <t>163分钟</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>08:41采样：该车到重点站丁香路锦绣路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±12分钟</t>
+          <t>09:12采样：该车到重点站金杨路金口路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数45分钟，约±9分钟</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6010,7 +6026,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -6020,7 +6036,7 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
@@ -6045,12 +6061,12 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -6063,7 +6079,7 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -6073,7 +6089,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -6083,44 +6099,40 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq41，推进3站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>183分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>08:31采样：该车到重点站康沈路秀康路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数133分钟，约±15分钟</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6128,13 +6140,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R46" s="2" t="inlineStr"/>
-      <c r="S46" s="2" t="inlineStr"/>
-      <c r="T46" s="2" t="inlineStr"/>
-      <c r="U46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq38（站名待映射） ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -6144,17 +6172,17 @@
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -6164,17 +6192,13 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC46" s="2" t="inlineStr">
-        <is>
-          <t>183.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>21/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6211,7 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -6197,7 +6221,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -6217,34 +6241,34 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr"/>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>08:41采样：该车到重点站白桦路明月路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数91分钟，约±9分钟</t>
+          <t>09:12采样：该车到重点站沪南路御桥路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±6分钟</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6258,7 +6282,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6293,12 +6317,12 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -6311,7 +6335,7 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -6321,7 +6345,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -6341,34 +6365,34 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>173分钟</t>
+          <t>168分钟</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr"/>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>08:41采样：该车到重点站沪南路华夏西路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数108分钟，约±12分钟</t>
+          <t>09:12采样：该车到重点站迎春路金松路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±8分钟</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6382,7 +6406,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6392,7 +6416,7 @@
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
@@ -6417,12 +6441,12 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>173.0</t>
+          <t>168.0</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>20/27</t>
+          <t>19/27</t>
         </is>
       </c>
     </row>
@@ -6435,7 +6459,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -6445,7 +6469,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6465,34 +6489,34 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr"/>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>08:41采样：该车到重点站金杨路云山路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数97分钟，约±8分钟</t>
+          <t>09:12采样：该车到重点站沪南路北中路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±12分钟</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6506,7 +6530,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6516,7 +6540,7 @@
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
@@ -6541,12 +6565,12 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6583,7 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -6569,7 +6593,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -6589,30 +6613,34 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>173分钟</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr"/>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr"/>
+          <t>09:12采样：该车到重点站迎春路金松路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±9分钟</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6626,7 +6654,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6636,17 +6664,17 @@
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6656,13 +6684,17 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC50" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>173.0</t>
+        </is>
+      </c>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>21/27</t>
         </is>
       </c>
     </row>
@@ -6675,24 +6707,24 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -6705,34 +6737,34 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>150分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr"/>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>08:41采样：该车到重点站康沈路秀康路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数121分钟，约±7分钟</t>
+          <t>09:12采样：该车到重点站沪南路北中路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6746,7 +6778,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6781,12 +6813,12 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -6799,24 +6831,24 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>08:20</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -6829,30 +6861,34 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>167分钟</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr"/>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr"/>
+          <t>09:12采样：该车到重点站沪南路高科西路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数89分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6866,7 +6902,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6876,17 +6912,17 @@
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6896,13 +6932,17 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC52" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>167.0</t>
+        </is>
+      </c>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>18/27</t>
         </is>
       </c>
     </row>
@@ -6915,24 +6955,24 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -6945,19 +6985,19 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>08:41采样：该车到重点站川周公路康沈路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数138分钟，约±5分钟</t>
+          <t>09:12采样：该车到重点站浦建路锦绣路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6967,12 +7007,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6986,7 +7026,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -7021,12 +7061,12 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -7039,22 +7079,22 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>08:35</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -7092,7 +7132,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -7106,7 +7146,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -7155,7 +7195,7 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -7165,7 +7205,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -7185,34 +7225,34 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr"/>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数139分钟估算，约±14分钟</t>
+          <t>09:12采样：该车到重点站沪南路华夏西路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数97分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7226,7 +7266,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7236,12 +7276,12 @@
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -7251,22 +7291,22 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>14/27</t>
         </is>
       </c>
     </row>
@@ -7279,7 +7319,7 @@
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -7289,7 +7329,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -7309,26 +7349,22 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数142分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7336,7 +7372,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7350,7 +7386,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7360,37 +7396,33 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC56" s="2" t="inlineStr">
-        <is>
-          <t>147.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -7403,7 +7435,7 @@
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -7413,7 +7445,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -7433,24 +7465,24 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数144分钟估算，约±8分钟</t>
+          <t>09:12采样：该车到重点站沪南路华夏西路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数96分钟，约±6分钟</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
@@ -7460,7 +7492,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7474,7 +7506,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7489,7 +7521,7 @@
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7499,22 +7531,22 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7559,7 @@
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -7537,7 +7569,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -7557,26 +7589,22 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数146分钟估算，约±8分钟</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7584,7 +7612,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7598,47 +7626,43 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>终点确认到达+2分钟（覆盖计划时间）</t>
+          <t>计划发车</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="inlineStr">
-        <is>
-          <t>158.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr"/>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -7651,24 +7675,24 @@
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -7681,22 +7705,26 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数139分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7704,7 +7732,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7718,7 +7746,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7728,17 +7756,17 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7748,13 +7776,17 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC59" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>133.5</t>
+        </is>
+      </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -7767,24 +7799,24 @@
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -7797,30 +7829,34 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="inlineStr"/>
+          <t>09:12采样：该车到重点站莱阳路东陆路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7834,7 +7870,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7844,17 +7880,17 @@
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7864,45 +7900,45 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>14/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7912,39 +7948,39 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+          <t>09:12采样：该车到重点站康丽路康恩路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数139分钟，约±7分钟</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7958,7 +7994,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7968,12 +8004,12 @@
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7993,40 +8029,40 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -8036,39 +8072,39 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>109分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr"/>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数146分钟估算，约±8分钟</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8082,7 +8118,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -8092,12 +8128,12 @@
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -8117,40 +8153,40 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>154.5</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -8160,39 +8196,35 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>113分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr"/>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8206,7 +8238,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -8216,17 +8248,17 @@
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -8236,45 +8268,41 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC63" s="2" t="inlineStr">
-        <is>
-          <t>101.5</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr"/>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -8284,39 +8312,35 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr"/>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N64" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8330,7 +8354,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8340,17 +8364,17 @@
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8360,45 +8384,45 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/27</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -8413,30 +8437,34 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr"/>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N65" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数145分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8450,7 +8478,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8460,61 +8488,65 @@
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC65" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>147.5</t>
+        </is>
+      </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8524,39 +8556,39 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr"/>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±8分钟</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8570,7 +8602,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8580,12 +8612,12 @@
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8605,40 +8637,40 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>06:55</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8648,39 +8680,39 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>114分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr"/>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数128分钟估算，约±5分钟</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8694,7 +8726,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>06:55</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8704,12 +8736,12 @@
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8724,17 +8756,17 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -8747,24 +8779,24 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -8777,34 +8809,34 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr"/>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8818,7 +8850,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8848,17 +8880,17 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -8871,7 +8903,7 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -8881,7 +8913,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -8896,35 +8928,39 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>117分钟</t>
+          <t>109分钟</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr"/>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:40采样，终点ETA 26分钟</t>
-        </is>
-      </c>
-      <c r="N69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8938,7 +8974,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8948,12 +8984,12 @@
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
@@ -8963,22 +8999,22 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB69" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8991,24 +9027,24 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -9021,34 +9057,34 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>113分钟</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -9062,7 +9098,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -9092,17 +9128,17 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -9115,24 +9151,24 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A58633D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>07:20</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -9140,39 +9176,39 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>105分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>08:40采样：该车到重点站丁香路金松路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数6分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9186,7 +9222,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -9196,12 +9232,12 @@
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
@@ -9211,22 +9247,22 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9239,7 +9275,7 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -9249,7 +9285,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -9269,34 +9305,30 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站五莲路归昌路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数25分钟，约±12分钟</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr"/>
       <c r="O72" s="2" t="inlineStr">
         <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
           <t>06:10</t>
-        </is>
-      </c>
-      <c r="P72" s="2" t="inlineStr">
-        <is>
-          <t>08:40</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9310,7 +9342,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9320,17 +9352,17 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -9340,17 +9372,13 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC72" s="2" t="inlineStr">
-        <is>
-          <t>81.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr"/>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -9363,7 +9391,7 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -9373,7 +9401,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9388,35 +9416,39 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:40采样，终点ETA 30分钟</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9430,7 +9462,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9440,12 +9472,12 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
@@ -9465,12 +9497,12 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9483,7 +9515,7 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -9493,7 +9525,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:55</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -9508,39 +9540,39 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>114分钟</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>08:40采样：该车到重点站五莲路荷泽路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数31分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9554,7 +9586,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:55</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9564,12 +9596,12 @@
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
@@ -9579,22 +9611,22 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9607,7 +9639,7 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -9617,7 +9649,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -9632,39 +9664,39 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>08:40采样：该车到重点站金高路俱进路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±6分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9678,7 +9710,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9688,12 +9720,12 @@
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
@@ -9703,22 +9735,22 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9731,7 +9763,7 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A66373D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -9741,7 +9773,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -9756,35 +9788,39 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>112分钟</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9798,7 +9834,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9808,33 +9844,37 @@
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC76" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -9847,7 +9887,7 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -9857,7 +9897,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -9872,39 +9912,39 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>08:40采样：该车到重点站巨峰路成园路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数45分钟，约±8分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9918,7 +9958,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9928,12 +9968,12 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -9953,12 +9993,12 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9971,7 +10011,7 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A58633D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -9981,7 +10021,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -10001,34 +10041,30 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>114分钟</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>08:40采样：该车到重点站金高路俱进路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:50采样，终点ETA 24分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr"/>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10042,7 +10078,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -10052,12 +10088,12 @@
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -10067,22 +10103,22 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -10095,7 +10131,7 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -10105,7 +10141,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -10125,34 +10161,30 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>107分钟</t>
+          <t>109分钟</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>08:40采样：该车到重点站杨高北路夏碧路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数77分钟，约±13分钟</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:00采样，终点ETA 18分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr"/>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10166,7 +10198,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -10176,12 +10208,12 @@
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
@@ -10201,12 +10233,12 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -10219,7 +10251,7 @@
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -10229,7 +10261,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -10244,39 +10276,39 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr"/>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>08:40采样：该车到重点站五莲路荷泽路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10290,7 +10322,7 @@
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
@@ -10300,12 +10332,12 @@
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
@@ -10325,12 +10357,12 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -10343,7 +10375,7 @@
       <c r="B81" s="2" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A53629D</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -10353,7 +10385,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -10368,39 +10400,39 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr"/>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±6分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10414,7 +10446,7 @@
       <c r="U81" s="2" t="inlineStr"/>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
@@ -10424,12 +10456,12 @@
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10439,22 +10471,22 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD81" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -10467,7 +10499,7 @@
       <c r="B82" s="2" t="inlineStr"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -10477,7 +10509,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -10492,39 +10524,39 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr"/>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>08:40采样：该车到重点站五莲路荷泽路 ETA 26分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -10538,7 +10570,7 @@
       <c r="U82" s="2" t="inlineStr"/>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
@@ -10548,12 +10580,12 @@
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
@@ -10563,22 +10595,22 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AD82" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -10591,24 +10623,24 @@
       <c r="B83" s="2" t="inlineStr"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A66373D</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -10621,26 +10653,22 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>103分钟</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr"/>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±12分钟</t>
-        </is>
-      </c>
-      <c r="N83" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:10采样，终点ETA 26分钟</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr"/>
       <c r="O83" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -10648,7 +10676,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10662,7 +10690,7 @@
       <c r="U83" s="2" t="inlineStr"/>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
@@ -10677,7 +10705,7 @@
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
@@ -10687,22 +10715,22 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -10715,24 +10743,24 @@
       <c r="B84" s="2" t="inlineStr"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -10745,30 +10773,30 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr"/>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：09:10采样，终点ETA 19分钟</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr"/>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10782,7 +10810,7 @@
       <c r="U84" s="2" t="inlineStr"/>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
@@ -10792,17 +10820,17 @@
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
@@ -10812,17 +10840,17 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -10835,24 +10863,24 @@
       <c r="B85" s="2" t="inlineStr"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A57902D</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>08:57</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -10865,30 +10893,34 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr"/>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N85" s="2" t="inlineStr"/>
+          <t>09:10采样：该车到重点站金杨路金桥路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数23分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -10902,7 +10934,7 @@
       <c r="U85" s="2" t="inlineStr"/>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
@@ -10912,22 +10944,22 @@
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
@@ -10937,12 +10969,12 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -10955,7 +10987,7 @@
       <c r="B86" s="2" t="inlineStr"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -10965,7 +10997,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -10985,30 +11017,34 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr"/>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N86" s="2" t="inlineStr"/>
+          <t>09:10采样：该车到重点站五莲路凌河路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±11分钟</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -11022,7 +11058,7 @@
       <c r="U86" s="2" t="inlineStr"/>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
@@ -11032,17 +11068,17 @@
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA86" s="2" t="inlineStr">
@@ -11052,17 +11088,17 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AD86" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -11075,7 +11111,7 @@
       <c r="B87" s="2" t="inlineStr"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -11085,7 +11121,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -11105,34 +11141,34 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr"/>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数91分钟估算，约±11分钟</t>
+          <t>09:10采样：该车到重点站金高路东靖路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -11146,7 +11182,7 @@
       <c r="U87" s="2" t="inlineStr"/>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="W87" s="2" t="inlineStr">
@@ -11156,12 +11192,12 @@
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -11171,22 +11207,22 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB87" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AD87" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -11199,7 +11235,7 @@
       <c r="B88" s="2" t="inlineStr"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -11209,7 +11245,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -11229,34 +11265,34 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr"/>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数91分钟估算，约±15分钟</t>
+          <t>08:50采样：该车到重点站航津路地铁站 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11270,47 +11306,1407 @@
       <c r="U88" s="2" t="inlineStr"/>
       <c r="V88" s="2" t="inlineStr">
         <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD88" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>09:10采样：该车到重点站金高路东靖路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数39分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD89" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>09:10采样：该车到重点站张杨北路博兴路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>99.5</t>
+        </is>
+      </c>
+      <c r="AD90" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>100分钟</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>09:10采样：该车到重点站金高路行泰路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±14分钟</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>97.5</t>
+        </is>
+      </c>
+      <c r="AD91" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>09:10采样：该车到重点站张杨北路博兴路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±11分钟</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AD92" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>96分钟</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>09:10采样：该车到重点站金高路行泰路 ETA 47分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AD93" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>09:10采样：该车到重点站丁香路长柳路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±9分钟</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AD94" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr"/>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AD95" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr"/>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
           <t>09:30</t>
         </is>
       </c>
-      <c r="W88" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X88" s="2" t="inlineStr">
+      <c r="X96" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="Y88" s="2" t="inlineStr">
+      <c r="Y96" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Z88" s="2" t="inlineStr">
+      <c r="Z96" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="AA88" s="2" t="inlineStr">
+      <c r="AA96" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB88" s="2" t="inlineStr">
+      <c r="AB96" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AC88" s="2" t="inlineStr">
-        <is>
-          <t>96.0</t>
-        </is>
-      </c>
-      <c r="AD88" s="2" t="inlineStr">
-        <is>
-          <t>8/18</t>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="AD96" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr"/>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>91分钟</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数91分钟估算，约±15分钟</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AD97" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr"/>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr"/>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
+      <c r="AD98" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr"/>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr"/>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr"/>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="AD99" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-operations.xlsx
+++ b/data/export/2026-09-22-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD301"/>
+  <dimension ref="A1:AD302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -454,7 +454,7 @@
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
     <col width="14" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
     <col width="18" customWidth="1" min="28" max="28"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1721,12 +1721,12 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2093,12 +2093,12 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AD22" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3581,12 +3581,12 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3776,7 +3776,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AD36" s="2" t="inlineStr">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5053,7 +5053,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD37" s="2" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5177,12 +5177,12 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AD45" s="2" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6169,12 +6169,12 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6417,7 +6417,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
@@ -6988,7 +6988,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AD53" s="2" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
@@ -7484,7 +7484,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7533,12 +7533,12 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
@@ -7980,7 +7980,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -8029,7 +8029,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AD61" s="2" t="inlineStr">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8277,7 +8277,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
@@ -8476,7 +8476,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8525,12 +8525,12 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8649,12 +8649,12 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8773,7 +8773,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9637,7 +9637,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
@@ -9960,7 +9960,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -10009,12 +10009,12 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -10080,7 +10080,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10129,7 +10129,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
@@ -10204,7 +10204,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
@@ -10328,7 +10328,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10377,7 +10377,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -10948,7 +10948,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD85" s="2" t="inlineStr">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11365,7 +11365,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AD88" s="2" t="inlineStr">
@@ -11413,12 +11413,12 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr"/>
@@ -11440,7 +11440,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -11489,7 +11489,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AD89" s="2" t="inlineStr">
@@ -11537,24 +11537,24 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>20:48</t>
+          <t>20:46</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr"/>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11613,7 +11613,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD90" s="2" t="inlineStr">
@@ -11688,7 +11688,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -11780,29 +11780,29 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站唐陆公路川桥路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±12分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
@@ -11812,7 +11812,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11836,12 +11836,12 @@
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11861,12 +11861,12 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -11904,12 +11904,12 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -11921,10 +11921,14 @@
       <c r="L93" s="2" t="inlineStr"/>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:21采样，终点ETA 40分钟</t>
-        </is>
-      </c>
-      <c r="N93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -11932,7 +11936,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11956,12 +11960,12 @@
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11981,7 +11985,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
@@ -12024,29 +12028,29 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:18</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr"/>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站博兴路东陆路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±11分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
@@ -12056,7 +12060,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12080,12 +12084,12 @@
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -12105,7 +12109,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD94" s="2" t="inlineStr">
@@ -12148,29 +12152,29 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>21:40</t>
+          <t>21:44</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数70分钟估算，约±12分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
@@ -12180,7 +12184,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12204,12 +12208,12 @@
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -12229,7 +12233,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
@@ -12277,26 +12281,22 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>22:05</t>
+          <t>22:04</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr"/>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数75分钟估算，约±8分钟</t>
-        </is>
-      </c>
-      <c r="N96" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:22采样，终点ETA 42分钟</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr"/>
       <c r="O96" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -12304,7 +12304,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12328,12 +12328,12 @@
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -12406,19 +12406,19 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr"/>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数71分钟估算，约±10分钟</t>
+          <t>21:22采样：该车到重点站长岛路台儿庄路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±9分钟</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
@@ -12428,7 +12428,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12457,7 +12457,7 @@
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -12477,7 +12477,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -12676,7 +12676,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12725,12 +12725,12 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>136.8</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -12854,7 +12854,7 @@
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -12978,7 +12978,7 @@
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -13176,7 +13176,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13225,7 +13225,7 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>143.2</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AD103" s="2" t="inlineStr">
@@ -13354,7 +13354,7 @@
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -13478,7 +13478,7 @@
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -13602,7 +13602,7 @@
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -13672,7 +13672,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13726,7 +13726,7 @@
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -13850,7 +13850,7 @@
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -13986,7 +13986,7 @@
       </c>
       <c r="AD109" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="AD110" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -14172,7 +14172,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14221,7 +14221,7 @@
       </c>
       <c r="AC111" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.2</t>
         </is>
       </c>
       <c r="AD111" s="2" t="inlineStr">
@@ -14292,7 +14292,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -14357,12 +14357,12 @@
       </c>
       <c r="AC112" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -14432,7 +14432,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -14481,12 +14481,12 @@
       </c>
       <c r="AC113" s="2" t="inlineStr">
         <is>
-          <t>139.2</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -14606,7 +14606,7 @@
       </c>
       <c r="AD114" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -14730,7 +14730,7 @@
       </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -14800,7 +14800,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14849,12 +14849,12 @@
       </c>
       <c r="AC116" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AD116" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -14920,7 +14920,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -14969,12 +14969,12 @@
       </c>
       <c r="AC117" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AD117" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -15044,7 +15044,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15093,12 +15093,12 @@
       </c>
       <c r="AC118" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -15222,7 +15222,7 @@
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -15288,7 +15288,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -15337,7 +15337,7 @@
       </c>
       <c r="AC120" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>144.7</t>
         </is>
       </c>
       <c r="AD120" s="2" t="inlineStr">
@@ -15412,7 +15412,7 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -15466,7 +15466,7 @@
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -15590,7 +15590,7 @@
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -15656,7 +15656,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -15705,12 +15705,12 @@
       </c>
       <c r="AC123" s="2" t="inlineStr">
         <is>
-          <t>145.7</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -15904,7 +15904,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -15953,12 +15953,12 @@
       </c>
       <c r="AC125" s="2" t="inlineStr">
         <is>
-          <t>136.8</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="AD126" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -16206,7 +16206,7 @@
       </c>
       <c r="AD127" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -16326,7 +16326,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -16528,7 +16528,7 @@
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
@@ -16577,7 +16577,7 @@
       </c>
       <c r="AC130" s="2" t="inlineStr">
         <is>
-          <t>143.2</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AD130" s="2" t="inlineStr">
@@ -16706,7 +16706,7 @@
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -16826,7 +16826,7 @@
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -16950,7 +16950,7 @@
       </c>
       <c r="AD133" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -17020,7 +17020,7 @@
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
@@ -17074,7 +17074,7 @@
       </c>
       <c r="AD134" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -17144,7 +17144,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17198,7 +17198,7 @@
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -17264,7 +17264,7 @@
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
@@ -17313,7 +17313,7 @@
       </c>
       <c r="AC136" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.2</t>
         </is>
       </c>
       <c r="AD136" s="2" t="inlineStr">
@@ -17442,7 +17442,7 @@
       </c>
       <c r="AD137" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -17562,7 +17562,7 @@
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -17632,7 +17632,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -17681,12 +17681,12 @@
       </c>
       <c r="AC139" s="2" t="inlineStr">
         <is>
-          <t>139.2</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -17752,7 +17752,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -17801,12 +17801,12 @@
       </c>
       <c r="AC140" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -17930,7 +17930,7 @@
       </c>
       <c r="AD141" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -18000,7 +18000,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -18049,12 +18049,12 @@
       </c>
       <c r="AC142" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -18124,7 +18124,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -18173,12 +18173,12 @@
       </c>
       <c r="AC143" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AD143" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -18302,7 +18302,7 @@
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -18372,7 +18372,7 @@
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q145" s="2" t="inlineStr">
@@ -18426,7 +18426,7 @@
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -18674,7 +18674,7 @@
       </c>
       <c r="AD147" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -18798,7 +18798,7 @@
       </c>
       <c r="AD148" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -18868,7 +18868,7 @@
       </c>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q149" s="2" t="inlineStr">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="AC149" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>144.7</t>
         </is>
       </c>
       <c r="AD149" s="2" t="inlineStr">
@@ -19046,7 +19046,7 @@
       </c>
       <c r="AD150" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -19170,7 +19170,7 @@
       </c>
       <c r="AD151" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -19236,7 +19236,7 @@
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q152" s="2" t="inlineStr">
@@ -19418,7 +19418,7 @@
       </c>
       <c r="AD153" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -19542,7 +19542,7 @@
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -19612,7 +19612,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q155" s="2" t="inlineStr">
@@ -19661,12 +19661,12 @@
       </c>
       <c r="AC155" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AD155" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -19790,7 +19790,7 @@
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -20038,7 +20038,7 @@
       </c>
       <c r="AD158" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -20108,7 +20108,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -20157,12 +20157,12 @@
       </c>
       <c r="AC159" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -20410,7 +20410,7 @@
       </c>
       <c r="AD161" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -20534,7 +20534,7 @@
       </c>
       <c r="AD162" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -20658,7 +20658,7 @@
       </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -20782,7 +20782,7 @@
       </c>
       <c r="AD164" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -20906,7 +20906,7 @@
       </c>
       <c r="AD165" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -21030,7 +21030,7 @@
       </c>
       <c r="AD166" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -21232,7 +21232,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q168" s="2" t="inlineStr">
@@ -21286,7 +21286,7 @@
       </c>
       <c r="AD168" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -21356,7 +21356,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q169" s="2" t="inlineStr">
@@ -21405,12 +21405,12 @@
       </c>
       <c r="AC169" s="2" t="inlineStr">
         <is>
-          <t>145.7</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AD169" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -21480,7 +21480,7 @@
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -21529,7 +21529,7 @@
       </c>
       <c r="AC170" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.2</t>
         </is>
       </c>
       <c r="AD170" s="2" t="inlineStr">
@@ -21604,7 +21604,7 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -21653,12 +21653,12 @@
       </c>
       <c r="AC171" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -21724,7 +21724,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -21840,7 +21840,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21889,12 +21889,12 @@
       </c>
       <c r="AC173" s="2" t="inlineStr">
         <is>
-          <t>136.8</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AD173" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -21964,7 +21964,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -22013,12 +22013,12 @@
       </c>
       <c r="AC174" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -22084,7 +22084,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -22133,7 +22133,7 @@
       </c>
       <c r="AC175" s="2" t="inlineStr">
         <is>
-          <t>143.2</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AD175" s="2" t="inlineStr">
@@ -22208,7 +22208,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22262,7 +22262,7 @@
       </c>
       <c r="AD176" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -22332,7 +22332,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22386,7 +22386,7 @@
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -22510,7 +22510,7 @@
       </c>
       <c r="AD178" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -22634,7 +22634,7 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -22758,7 +22758,7 @@
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -22882,7 +22882,7 @@
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -22952,7 +22952,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
@@ -23001,12 +23001,12 @@
       </c>
       <c r="AC182" s="2" t="inlineStr">
         <is>
-          <t>139.2</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AD182" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -23130,7 +23130,7 @@
       </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -23254,7 +23254,7 @@
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -23378,7 +23378,7 @@
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -23502,7 +23502,7 @@
       </c>
       <c r="AD186" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -23626,7 +23626,7 @@
       </c>
       <c r="AD187" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -23696,7 +23696,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q188" s="2" t="inlineStr">
@@ -23745,12 +23745,12 @@
       </c>
       <c r="AC188" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AD188" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -23793,24 +23793,24 @@
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="K189" s="2" t="inlineStr"/>
       <c r="L189" s="2" t="inlineStr"/>
       <c r="M189" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N189" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O189" s="2" t="inlineStr">
@@ -23820,7 +23820,7 @@
       </c>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q189" s="2" t="inlineStr">
@@ -23869,7 +23869,7 @@
       </c>
       <c r="AC189" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>144.7</t>
         </is>
       </c>
       <c r="AD189" s="2" t="inlineStr">
@@ -23917,26 +23917,22 @@
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K190" s="2" t="inlineStr"/>
       <c r="L190" s="2" t="inlineStr"/>
       <c r="M190" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站康沈路秀沿路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±7分钟</t>
-        </is>
-      </c>
-      <c r="N190" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：20:40采样，终点ETA 11分钟</t>
+        </is>
+      </c>
+      <c r="N190" s="2" t="inlineStr"/>
       <c r="O190" s="2" t="inlineStr">
         <is>
           <t>17:51</t>
@@ -23944,7 +23940,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -23973,7 +23969,7 @@
       </c>
       <c r="Y190" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z190" s="2" t="inlineStr">
@@ -23993,12 +23989,12 @@
       </c>
       <c r="AC190" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD190" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -24036,29 +24032,29 @@
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>21:07</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K191" s="2" t="inlineStr"/>
       <c r="L191" s="2" t="inlineStr"/>
       <c r="M191" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站金杨路金口路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N191" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O191" s="2" t="inlineStr">
@@ -24068,7 +24064,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q191" s="2" t="inlineStr">
@@ -24092,12 +24088,12 @@
       </c>
       <c r="X191" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y191" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z191" s="2" t="inlineStr">
@@ -24117,12 +24113,12 @@
       </c>
       <c r="AC191" s="2" t="inlineStr">
         <is>
-          <t>145.7</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AD191" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -24160,7 +24156,7 @@
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
@@ -24177,12 +24173,12 @@
       <c r="L192" s="2" t="inlineStr"/>
       <c r="M192" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站沪南路北中路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N192" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O192" s="2" t="inlineStr">
@@ -24192,7 +24188,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q192" s="2" t="inlineStr">
@@ -24216,12 +24212,12 @@
       </c>
       <c r="X192" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y192" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z192" s="2" t="inlineStr">
@@ -24246,7 +24242,7 @@
       </c>
       <c r="AD192" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -24284,29 +24280,29 @@
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>21:26</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K193" s="2" t="inlineStr"/>
       <c r="L193" s="2" t="inlineStr"/>
       <c r="M193" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站锦绣路罗山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±11分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N193" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O193" s="2" t="inlineStr">
@@ -24316,7 +24312,7 @@
       </c>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q193" s="2" t="inlineStr">
@@ -24340,12 +24336,12 @@
       </c>
       <c r="X193" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y193" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z193" s="2" t="inlineStr">
@@ -24365,12 +24361,12 @@
       </c>
       <c r="AC193" s="2" t="inlineStr">
         <is>
-          <t>136.8</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AD193" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -24408,29 +24404,29 @@
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K194" s="2" t="inlineStr"/>
       <c r="L194" s="2" t="inlineStr"/>
       <c r="M194" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站浦建路锦绣路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N194" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O194" s="2" t="inlineStr">
@@ -24440,7 +24436,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr">
@@ -24464,12 +24460,12 @@
       </c>
       <c r="X194" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y194" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z194" s="2" t="inlineStr">
@@ -24489,7 +24485,7 @@
       </c>
       <c r="AC194" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.2</t>
         </is>
       </c>
       <c r="AD194" s="2" t="inlineStr">
@@ -24537,19 +24533,19 @@
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K195" s="2" t="inlineStr"/>
       <c r="L195" s="2" t="inlineStr"/>
       <c r="M195" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站锦绣路花木路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数72分钟，约±5分钟</t>
+          <t>20:40采样：该车到重点站云山路碧云路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N195" s="2" t="inlineStr">
@@ -24564,7 +24560,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q195" s="2" t="inlineStr">
@@ -24613,12 +24609,12 @@
       </c>
       <c r="AC195" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AD195" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -24651,12 +24647,12 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq28推进至seq52，推进24站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
@@ -24684,7 +24680,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q196" s="2" t="inlineStr">
@@ -24692,10 +24688,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R196" s="2" t="inlineStr"/>
-      <c r="S196" s="2" t="inlineStr"/>
-      <c r="T196" s="2" t="inlineStr"/>
-      <c r="U196" s="2" t="inlineStr"/>
+      <c r="R196" s="2" t="inlineStr">
+        <is>
+          <t>物理seq31（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S196" s="2" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="T196" s="2" t="inlineStr">
+        <is>
+          <t>20:27</t>
+        </is>
+      </c>
+      <c r="U196" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq31映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V196" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -24713,7 +24725,7 @@
       </c>
       <c r="Y196" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z196" s="2" t="inlineStr">
@@ -24738,7 +24750,7 @@
       </c>
       <c r="AD196" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -24786,21 +24798,17 @@
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K197" s="2" t="inlineStr"/>
       <c r="L197" s="2" t="inlineStr"/>
       <c r="M197" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站沪南路华夏西路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±6分钟</t>
-        </is>
-      </c>
-      <c r="N197" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:21采样，终点ETA 28分钟</t>
+        </is>
+      </c>
+      <c r="N197" s="2" t="inlineStr"/>
       <c r="O197" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -24808,7 +24816,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -24832,12 +24840,12 @@
       </c>
       <c r="X197" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y197" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z197" s="2" t="inlineStr">
@@ -24857,7 +24865,7 @@
       </c>
       <c r="AC197" s="2" t="inlineStr">
         <is>
-          <t>143.2</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AD197" s="2" t="inlineStr">
@@ -24900,29 +24908,29 @@
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>21:43</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K198" s="2" t="inlineStr"/>
       <c r="L198" s="2" t="inlineStr"/>
       <c r="M198" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站白桦路明月路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数79分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N198" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O198" s="2" t="inlineStr">
@@ -24932,7 +24940,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
@@ -24956,12 +24964,12 @@
       </c>
       <c r="X198" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y198" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z198" s="2" t="inlineStr">
@@ -24981,12 +24989,12 @@
       </c>
       <c r="AC198" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AD198" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -25029,24 +25037,24 @@
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>22:05</t>
+          <t>22:06</t>
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K199" s="2" t="inlineStr"/>
       <c r="L199" s="2" t="inlineStr"/>
       <c r="M199" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站博兴路兰城路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数104分钟，约±9分钟</t>
+          <t>21:21采样：该车到重点站沪南路御桥路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±7分钟</t>
         </is>
       </c>
       <c r="N199" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O199" s="2" t="inlineStr">
@@ -25056,7 +25064,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -25105,12 +25113,12 @@
       </c>
       <c r="AC199" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AD199" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -25165,7 +25173,7 @@
       <c r="L200" s="2" t="inlineStr"/>
       <c r="M200" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站川周公路康沈路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±5分钟</t>
+          <t>21:21采样：该车到重点站云山路碧云路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N200" s="2" t="inlineStr">
@@ -25180,7 +25188,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr">
@@ -25234,7 +25242,7 @@
       </c>
       <c r="AD200" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -25277,24 +25285,24 @@
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K201" s="2" t="inlineStr"/>
       <c r="L201" s="2" t="inlineStr"/>
       <c r="M201" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±5分钟</t>
+          <t>21:21采样：该车到重点站锦绣路花木路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数70分钟，约±6分钟</t>
         </is>
       </c>
       <c r="N201" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O201" s="2" t="inlineStr">
@@ -25304,7 +25312,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25333,7 +25341,7 @@
       </c>
       <c r="Y201" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z201" s="2" t="inlineStr">
@@ -25353,12 +25361,12 @@
       </c>
       <c r="AC201" s="2" t="inlineStr">
         <is>
-          <t>139.2</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AD201" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -25401,24 +25409,24 @@
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>117分钟</t>
         </is>
       </c>
       <c r="K202" s="2" t="inlineStr"/>
       <c r="L202" s="2" t="inlineStr"/>
       <c r="M202" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数125分钟估算，约±6分钟</t>
+          <t>21:21采样：该车到重点站沪南路华夏西路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±9分钟</t>
         </is>
       </c>
       <c r="N202" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O202" s="2" t="inlineStr">
@@ -25428,7 +25436,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
@@ -25457,7 +25465,7 @@
       </c>
       <c r="Y202" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z202" s="2" t="inlineStr">
@@ -25477,12 +25485,12 @@
       </c>
       <c r="AC202" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AD202" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -25552,7 +25560,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -25601,7 +25609,7 @@
       </c>
       <c r="AC203" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AD203" s="2" t="inlineStr">
@@ -25800,7 +25808,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q205" s="2" t="inlineStr">
@@ -25849,12 +25857,12 @@
       </c>
       <c r="AC205" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD205" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -25978,7 +25986,7 @@
       </c>
       <c r="AD206" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -26164,7 +26172,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q208" s="2" t="inlineStr">
@@ -26213,12 +26221,12 @@
       </c>
       <c r="AC208" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD208" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -26342,7 +26350,7 @@
       </c>
       <c r="AD209" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -26466,7 +26474,7 @@
       </c>
       <c r="AD210" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -26536,7 +26544,7 @@
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q211" s="2" t="inlineStr">
@@ -26575,22 +26583,22 @@
       </c>
       <c r="AA211" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB211" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC211" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="AD211" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -26660,7 +26668,7 @@
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q212" s="2" t="inlineStr">
@@ -26704,17 +26712,17 @@
       </c>
       <c r="AB212" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC212" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AD212" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -26834,7 +26842,7 @@
       </c>
       <c r="AD213" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -27078,7 +27086,7 @@
       </c>
       <c r="AD215" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -27202,7 +27210,7 @@
       </c>
       <c r="AD216" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -27396,7 +27404,7 @@
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q218" s="2" t="inlineStr">
@@ -27440,17 +27448,17 @@
       </c>
       <c r="AB218" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC218" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AD218" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -27520,7 +27528,7 @@
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q219" s="2" t="inlineStr">
@@ -27569,7 +27577,7 @@
       </c>
       <c r="AC219" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AD219" s="2" t="inlineStr">
@@ -27822,7 +27830,7 @@
       </c>
       <c r="AD221" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -28016,7 +28024,7 @@
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q223" s="2" t="inlineStr">
@@ -28065,12 +28073,12 @@
       </c>
       <c r="AC223" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD223" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -28194,7 +28202,7 @@
       </c>
       <c r="AD224" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -28264,7 +28272,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q225" s="2" t="inlineStr">
@@ -28313,12 +28321,12 @@
       </c>
       <c r="AC225" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD225" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -28442,7 +28450,7 @@
       </c>
       <c r="AD226" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -28562,7 +28570,7 @@
       </c>
       <c r="AD227" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -28632,7 +28640,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q228" s="2" t="inlineStr">
@@ -28676,17 +28684,17 @@
       </c>
       <c r="AB228" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC228" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AD228" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -28756,7 +28764,7 @@
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q229" s="2" t="inlineStr">
@@ -28795,22 +28803,22 @@
       </c>
       <c r="AA229" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB229" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC229" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="AD229" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -28930,7 +28938,7 @@
       </c>
       <c r="AD230" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -29178,7 +29186,7 @@
       </c>
       <c r="AD232" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -29244,7 +29252,7 @@
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q233" s="2" t="inlineStr">
@@ -29288,17 +29296,17 @@
       </c>
       <c r="AB233" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC233" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AD233" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -29546,7 +29554,7 @@
       </c>
       <c r="AD235" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -29736,7 +29744,7 @@
       </c>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q237" s="2" t="inlineStr">
@@ -29797,12 +29805,12 @@
       </c>
       <c r="AC237" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD237" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -29926,7 +29934,7 @@
       </c>
       <c r="AD238" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -29992,7 +30000,7 @@
       </c>
       <c r="P239" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q239" s="2" t="inlineStr">
@@ -30048,17 +30056,17 @@
       </c>
       <c r="AB239" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC239" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AD239" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -30182,7 +30190,7 @@
       </c>
       <c r="AD240" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -30306,7 +30314,7 @@
       </c>
       <c r="AD241" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -30430,7 +30438,7 @@
       </c>
       <c r="AD242" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -30926,7 +30934,7 @@
       </c>
       <c r="AD246" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -31050,7 +31058,7 @@
       </c>
       <c r="AD247" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -31174,7 +31182,7 @@
       </c>
       <c r="AD248" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -31298,7 +31306,7 @@
       </c>
       <c r="AD249" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -31422,7 +31430,7 @@
       </c>
       <c r="AD250" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -31790,7 +31798,7 @@
       </c>
       <c r="AD253" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -32034,7 +32042,7 @@
       </c>
       <c r="AD255" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -32104,7 +32112,7 @@
       </c>
       <c r="P256" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q256" s="2" t="inlineStr">
@@ -32153,7 +32161,7 @@
       </c>
       <c r="AC256" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AD256" s="2" t="inlineStr">
@@ -32282,7 +32290,7 @@
       </c>
       <c r="AD257" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -32406,7 +32414,7 @@
       </c>
       <c r="AD258" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -32530,7 +32538,7 @@
       </c>
       <c r="AD259" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -32654,7 +32662,7 @@
       </c>
       <c r="AD260" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -32724,7 +32732,7 @@
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q261" s="2" t="inlineStr">
@@ -32773,12 +32781,12 @@
       </c>
       <c r="AC261" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD261" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -32972,7 +32980,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q263" s="2" t="inlineStr">
@@ -33011,22 +33019,22 @@
       </c>
       <c r="AA263" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB263" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC263" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="AD263" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -33344,7 +33352,7 @@
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q266" s="2" t="inlineStr">
@@ -33393,12 +33401,12 @@
       </c>
       <c r="AC266" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD266" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -33468,7 +33476,7 @@
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q267" s="2" t="inlineStr">
@@ -33512,17 +33520,17 @@
       </c>
       <c r="AB267" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC267" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AD267" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -33770,7 +33778,7 @@
       </c>
       <c r="AD269" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -33840,7 +33848,7 @@
       </c>
       <c r="P270" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q270" s="2" t="inlineStr">
@@ -33884,17 +33892,17 @@
       </c>
       <c r="AB270" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC270" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AD270" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -34018,7 +34026,7 @@
       </c>
       <c r="AD271" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -34088,7 +34096,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q272" s="2" t="inlineStr">
@@ -34137,7 +34145,7 @@
       </c>
       <c r="AC272" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AD272" s="2" t="inlineStr">
@@ -34266,7 +34274,7 @@
       </c>
       <c r="AD273" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -34390,7 +34398,7 @@
       </c>
       <c r="AD274" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -34514,7 +34522,7 @@
       </c>
       <c r="AD275" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -34638,7 +34646,7 @@
       </c>
       <c r="AD276" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -34708,7 +34716,7 @@
       </c>
       <c r="P277" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q277" s="2" t="inlineStr">
@@ -34757,12 +34765,12 @@
       </c>
       <c r="AC277" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD277" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -34956,7 +34964,7 @@
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q279" s="2" t="inlineStr">
@@ -34995,22 +35003,22 @@
       </c>
       <c r="AA279" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB279" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC279" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="AD279" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -35328,7 +35336,7 @@
       </c>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q282" s="2" t="inlineStr">
@@ -35377,12 +35385,12 @@
       </c>
       <c r="AC282" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD282" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -35452,7 +35460,7 @@
       </c>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q283" s="2" t="inlineStr">
@@ -35496,17 +35504,17 @@
       </c>
       <c r="AB283" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC283" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AD283" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -35630,7 +35638,7 @@
       </c>
       <c r="AD284" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -35878,7 +35886,7 @@
       </c>
       <c r="AD286" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -35948,7 +35956,7 @@
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q287" s="2" t="inlineStr">
@@ -35992,17 +36000,17 @@
       </c>
       <c r="AB287" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC287" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AD287" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -36126,7 +36134,7 @@
       </c>
       <c r="AD288" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -36196,7 +36204,7 @@
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q289" s="2" t="inlineStr">
@@ -36245,7 +36253,7 @@
       </c>
       <c r="AC289" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AD289" s="2" t="inlineStr">
@@ -36374,7 +36382,7 @@
       </c>
       <c r="AD290" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -36498,7 +36506,7 @@
       </c>
       <c r="AD291" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -36692,7 +36700,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q293" s="2" t="inlineStr">
@@ -36741,12 +36749,12 @@
       </c>
       <c r="AC293" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD293" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -36789,24 +36797,24 @@
       </c>
       <c r="I294" s="2" t="inlineStr">
         <is>
-          <t>20:47</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="J294" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K294" s="2" t="inlineStr"/>
       <c r="L294" s="2" t="inlineStr"/>
       <c r="M294" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N294" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O294" s="2" t="inlineStr">
@@ -36816,7 +36824,7 @@
       </c>
       <c r="P294" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q294" s="2" t="inlineStr">
@@ -36865,12 +36873,12 @@
       </c>
       <c r="AC294" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD294" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -36908,27 +36916,31 @@
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I295" s="2" t="inlineStr">
         <is>
-          <t>20:54</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="J295" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K295" s="2" t="inlineStr"/>
       <c r="L295" s="2" t="inlineStr"/>
       <c r="M295" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:20采样，终点ETA 34分钟</t>
-        </is>
-      </c>
-      <c r="N295" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N295" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O295" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -36936,7 +36948,7 @@
       </c>
       <c r="P295" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q295" s="2" t="inlineStr">
@@ -36960,12 +36972,12 @@
       </c>
       <c r="X295" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y295" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z295" s="2" t="inlineStr">
@@ -36975,22 +36987,22 @@
       </c>
       <c r="AA295" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB295" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC295" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="AD295" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -37028,27 +37040,31 @@
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I296" s="2" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="J296" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K296" s="2" t="inlineStr"/>
       <c r="L296" s="2" t="inlineStr"/>
       <c r="M296" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:20采样，终点ETA 55分钟</t>
-        </is>
-      </c>
-      <c r="N296" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N296" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O296" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -37056,7 +37072,7 @@
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q296" s="2" t="inlineStr">
@@ -37080,17 +37096,17 @@
       </c>
       <c r="X296" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y296" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z296" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA296" s="2" t="inlineStr">
@@ -37100,17 +37116,17 @@
       </c>
       <c r="AB296" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC296" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AD296" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -37153,19 +37169,19 @@
       </c>
       <c r="I297" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:39</t>
         </is>
       </c>
       <c r="J297" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="K297" s="2" t="inlineStr"/>
       <c r="L297" s="2" t="inlineStr"/>
       <c r="M297" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：21:11采样，终点ETA 28分钟</t>
         </is>
       </c>
       <c r="N297" s="2" t="inlineStr"/>
@@ -37176,7 +37192,7 @@
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q297" s="2" t="inlineStr">
@@ -37200,17 +37216,17 @@
       </c>
       <c r="X297" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y297" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z297" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA297" s="2" t="inlineStr">
@@ -37220,17 +37236,17 @@
       </c>
       <c r="AB297" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC297" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AD297" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -37268,29 +37284,29 @@
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I298" s="2" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>21:39</t>
         </is>
       </c>
       <c r="J298" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K298" s="2" t="inlineStr"/>
       <c r="L298" s="2" t="inlineStr"/>
       <c r="M298" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站云山路灵山路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±11分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N298" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O298" s="2" t="inlineStr">
@@ -37300,7 +37316,7 @@
       </c>
       <c r="P298" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q298" s="2" t="inlineStr">
@@ -37324,12 +37340,12 @@
       </c>
       <c r="X298" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y298" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z298" s="2" t="inlineStr">
@@ -37349,7 +37365,7 @@
       </c>
       <c r="AC298" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AD298" s="2" t="inlineStr">
@@ -37392,29 +37408,29 @@
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I299" s="2" t="inlineStr">
         <is>
-          <t>22:04</t>
+          <t>21:58</t>
         </is>
       </c>
       <c r="J299" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K299" s="2" t="inlineStr"/>
       <c r="L299" s="2" t="inlineStr"/>
       <c r="M299" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N299" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O299" s="2" t="inlineStr">
@@ -37424,7 +37440,7 @@
       </c>
       <c r="P299" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q299" s="2" t="inlineStr">
@@ -37448,12 +37464,12 @@
       </c>
       <c r="X299" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y299" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z299" s="2" t="inlineStr">
@@ -37473,12 +37489,12 @@
       </c>
       <c r="AC299" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD299" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -37548,7 +37564,7 @@
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q300" s="2" t="inlineStr">
@@ -37587,22 +37603,22 @@
       </c>
       <c r="AA300" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB300" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC300" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="AD300" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -37615,7 +37631,7 @@
       <c r="B301" s="2" t="inlineStr"/>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>沪A66373D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
@@ -37645,30 +37661,34 @@
       </c>
       <c r="I301" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="J301" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K301" s="2" t="inlineStr"/>
       <c r="L301" s="2" t="inlineStr"/>
       <c r="M301" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N301" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="N301" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="O301" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q301" s="2" t="inlineStr">
@@ -37692,37 +37712,157 @@
       </c>
       <c r="X301" s="2" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y301" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z301" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA301" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB301" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC301" s="2" t="inlineStr">
+        <is>
+          <t>89.4</t>
+        </is>
+      </c>
+      <c r="AD301" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr"/>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>沪A66373D</t>
+        </is>
+      </c>
+      <c r="D302" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E302" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="F302" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G302" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H302" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I302" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J302" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K302" s="2" t="inlineStr"/>
+      <c r="L302" s="2" t="inlineStr"/>
+      <c r="M302" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N302" s="2" t="inlineStr"/>
+      <c r="O302" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P302" s="2" t="inlineStr">
+        <is>
+          <t>21:11</t>
+        </is>
+      </c>
+      <c r="Q302" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R302" s="2" t="inlineStr"/>
+      <c r="S302" s="2" t="inlineStr"/>
+      <c r="T302" s="2" t="inlineStr"/>
+      <c r="U302" s="2" t="inlineStr"/>
+      <c r="V302" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="W302" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X302" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y301" s="2" t="inlineStr">
+      <c r="Y302" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Z301" s="2" t="inlineStr">
+      <c r="Z302" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA301" s="2" t="inlineStr">
+      <c r="AA302" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AB301" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC301" s="2" t="inlineStr">
-        <is>
-          <t>81.2</t>
-        </is>
-      </c>
-      <c r="AD301" s="2" t="inlineStr">
-        <is>
-          <t>1/18</t>
+      <c r="AB302" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC302" s="2" t="inlineStr">
+        <is>
+          <t>85.2</t>
+        </is>
+      </c>
+      <c r="AD302" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
         </is>
       </c>
     </row>
